--- a/StructureDefinition-openelis-specimen.xlsx
+++ b/StructureDefinition-openelis-specimen.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3199" uniqueCount="542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3199" uniqueCount="543">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.2.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T02:24:20+00:00</t>
+    <t>2026-10-12T15:07:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1289,7 +1289,7 @@
     <t>Person who collected the specimen.</t>
   </si>
   <si>
-    <t>Not populated by OpenELIS today (see Known Issues).</t>
+    <t>Display only: the collector's name as entered.</t>
   </si>
   <si>
     <t>.participation[typeCode=PFM].role</t>
@@ -1346,6 +1346,10 @@
   </si>
   <si>
     <t>The quantity of specimen collected; for instance the volume of a blood sample, or the physical measurement of an anatomic pathology sample.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>.participation[typeCode=SBJ].role[classCode=SPEC].player.quantity</t>
@@ -1612,7 +1616,7 @@
     <t>The quantity of specimen in the container; may be volume, dimensions, or other appropriate measurements, depending on the specimen type.</t>
   </si>
   <si>
-    <t>code is the OpenELIS unit-of-measure name with system UCUM. Not every OpenELIS unit name is a valid UCUM code (see Known Issues).</t>
+    <t>unit is the OpenELIS unit-of-measure name. system UCUM and code are sent only when the unit has a valid UCUM code (its configured UCUM code, else its name); otherwise unit alone.</t>
   </si>
   <si>
     <t>SampleItem.quantity + unitOfMeasure</t>
@@ -9457,27 +9461,27 @@
         <v>78</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>101</v>
+        <v>431</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9503,13 +9507,13 @@
         <v>185</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9538,10 +9542,10 @@
         <v>276</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>78</v>
@@ -9559,7 +9563,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9574,24 +9578,24 @@
         <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9617,13 +9621,13 @@
         <v>185</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9652,10 +9656,10 @@
         <v>276</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>78</v>
@@ -9673,7 +9677,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9688,24 +9692,24 @@
         <v>101</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9728,19 +9732,19 @@
         <v>89</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>78</v>
@@ -9768,10 +9772,10 @@
         <v>190</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>78</v>
@@ -9789,7 +9793,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9813,15 +9817,15 @@
         <v>78</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9847,10 +9851,10 @@
         <v>386</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9901,7 +9905,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9919,7 +9923,7 @@
         <v>78</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>78</v>
@@ -9930,10 +9934,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10042,10 +10046,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10156,10 +10160,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10272,10 +10276,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10301,10 +10305,10 @@
         <v>161</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10355,7 +10359,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10373,7 +10377,7 @@
         <v>78</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>78</v>
@@ -10384,10 +10388,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10413,10 +10417,10 @@
         <v>185</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10446,10 +10450,10 @@
         <v>276</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>78</v>
@@ -10467,7 +10471,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10496,10 +10500,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10522,13 +10526,13 @@
         <v>78</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10579,7 +10583,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10597,21 +10601,21 @@
         <v>78</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10634,13 +10638,13 @@
         <v>78</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10691,7 +10695,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -10720,10 +10724,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10749,10 +10753,10 @@
         <v>386</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10803,7 +10807,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -10821,7 +10825,7 @@
         <v>78</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>78</v>
@@ -10832,10 +10836,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10944,10 +10948,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11058,10 +11062,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11174,10 +11178,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11203,10 +11207,10 @@
         <v>147</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11257,7 +11261,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11281,15 +11285,15 @@
         <v>78</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11315,10 +11319,10 @@
         <v>161</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11369,7 +11373,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -11387,7 +11391,7 @@
         <v>78</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>78</v>
@@ -11398,10 +11402,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11427,10 +11431,10 @@
         <v>185</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11442,7 +11446,7 @@
         <v>78</v>
       </c>
       <c r="S83" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="T83" t="s" s="2">
         <v>78</v>
@@ -11460,10 +11464,10 @@
         <v>276</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>78</v>
@@ -11481,7 +11485,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -11505,15 +11509,15 @@
         <v>78</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11539,10 +11543,10 @@
         <v>428</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -11593,7 +11597,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -11605,27 +11609,27 @@
         <v>78</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>101</v>
+        <v>431</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11651,13 +11655,13 @@
         <v>428</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -11707,7 +11711,7 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -11719,27 +11723,27 @@
         <v>78</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>101</v>
+        <v>431</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11762,13 +11766,13 @@
         <v>78</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -11798,10 +11802,10 @@
         <v>276</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>78</v>
@@ -11819,7 +11823,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -11837,21 +11841,21 @@
         <v>78</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11877,16 +11881,16 @@
         <v>185</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>78</v>
@@ -11914,10 +11918,10 @@
         <v>190</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>78</v>
@@ -11935,7 +11939,7 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -11950,7 +11954,7 @@
         <v>101</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>78</v>
@@ -11959,15 +11963,15 @@
         <v>78</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11990,13 +11994,13 @@
         <v>78</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="L88" t="s" s="2">
         <v>51</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12047,7 +12051,7 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12062,16 +12066,16 @@
         <v>101</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
   </sheetData>

--- a/StructureDefinition-openelis-specimen.xlsx
+++ b/StructureDefinition-openelis-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T15:07:11+00:00</t>
+    <t>2026-10-12T15:22:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-openelis-specimen.xlsx
+++ b/StructureDefinition-openelis-specimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.1</t>
+    <t>0.2.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T15:22:52+00:00</t>
+    <t>2026-10-14T21:19:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
